--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,60 +431,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -494,19 +504,33 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>7000</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -514,19 +538,33 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
         <v>7000</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -534,19 +572,33 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
         <v>7500</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -554,19 +606,33 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>7500</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -574,19 +640,33 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
         <v>7500</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -603,16 +683,28 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>15000</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>-40000</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -629,13 +721,26 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>15000</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -652,10 +757,24 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -663,16 +782,31 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -680,16 +814,31 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -697,16 +846,31 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -714,16 +878,31 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -731,16 +910,31 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -748,16 +942,31 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -765,16 +974,31 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -782,16 +1006,31 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -799,16 +1038,31 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -816,16 +1070,31 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,16 +1102,31 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -850,16 +1134,31 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,16 +1166,31 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -884,16 +1198,31 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -901,16 +1230,31 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -918,16 +1262,31 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -935,16 +1294,31 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -952,16 +1326,31 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -969,16 +1358,31 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -986,16 +1390,31 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1003,16 +1422,31 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1020,16 +1454,31 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1037,16 +1486,31 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1054,16 +1518,31 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1071,16 +1550,31 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1088,16 +1582,31 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1105,16 +1614,31 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1131,10 +1655,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,70 +431,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv fixed</t>
+          <t>big-ticket items</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>big-ticket items</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -504,33 +494,19 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
+      <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -538,33 +514,19 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
+      <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -572,33 +534,19 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -606,33 +554,19 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
+      <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -640,33 +574,19 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
+      <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,28 +603,16 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
         <v>15000</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-40000</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="P7" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -721,26 +629,13 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
         <v>15000</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -757,24 +652,10 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -782,31 +663,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -814,31 +680,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -846,31 +697,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -878,31 +714,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -910,31 +731,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,31 +748,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -974,31 +765,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1006,31 +782,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1038,31 +799,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1070,31 +816,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1102,31 +833,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,31 +850,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1166,31 +867,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1198,31 +884,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1230,31 +901,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1262,31 +918,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1294,31 +935,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1326,31 +952,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1358,31 +969,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1390,31 +986,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1422,31 +1003,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1454,31 +1020,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1486,31 +1037,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1518,31 +1054,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1550,31 +1071,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1582,31 +1088,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1614,31 +1105,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1655,6 +1131,10 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
